--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_352_R36.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_352_R36.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.196999999999999</v>
+        <v>8.7317</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1491</v>
+        <v>5.2552</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0479</v>
+        <v>3.4766</v>
       </c>
       <c r="G2" t="n">
         <v>3.4813</v>
@@ -610,13 +610,13 @@
         <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4115</v>
+        <v>0.9463</v>
       </c>
       <c r="T2" t="n">
-        <v>0.767</v>
+        <v>0.8731</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6445</v>
+        <v>0.0732</v>
       </c>
       <c r="V2" t="n">
         <v>2.6805</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8956</v>
+        <v>8.425800000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8938</v>
+        <v>4.2911</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0017</v>
+        <v>4.1347</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3412</v>
+        <v>3.9213</v>
       </c>
       <c r="H3" t="n">
-        <v>3.0262</v>
+        <v>0.8799</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3151</v>
+        <v>3.0414</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8411</v>
+        <v>2.9247</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7307</v>
+        <v>2.3429</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1104</v>
+        <v>0.5818</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5001</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7045</v>
+        <v>-1.463</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2046</v>
+        <v>2.4595</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1598</v>
+        <v>3.7112</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6266</v>
+        <v>0.3242</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1429</v>
+        <v>0.6137</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4837</v>
+        <v>-0.2895</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.8608</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1418</v>
+        <v>2.1444</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1418</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.2924</v>
+        <v>6.7167</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3593</v>
+        <v>4.9502</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9331</v>
+        <v>1.7665</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9213</v>
+        <v>4.3412</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8799</v>
+        <v>3.0262</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0414</v>
+        <v>1.3151</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9247</v>
+        <v>3.8411</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3429</v>
+        <v>3.7307</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5818</v>
+        <v>0.1104</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.5001</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.463</v>
+        <v>-0.7045</v>
       </c>
       <c r="O4" t="n">
-        <v>2.4595</v>
+        <v>1.2046</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R4" t="n">
-        <v>3.7112</v>
+        <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8092</v>
+        <v>1.4477</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3181</v>
+        <v>1.1993</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4911</v>
+        <v>0.2484</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8608</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1444</v>
+        <v>0.1418</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2836</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.2483</v>
+        <v>5.7598</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7406</v>
+        <v>2.8153</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5077</v>
+        <v>2.9445</v>
       </c>
       <c r="G5" t="n">
         <v>4.0647</v>
@@ -844,13 +844,13 @@
         <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6294999999999999</v>
+        <v>1.1411</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1325</v>
+        <v>1.2072</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.503</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1418</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.314</v>
+        <v>1.0081</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5064</v>
+        <v>0.066</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8076</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0.4837</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2968</v>
+        <v>0.9908</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5454</v>
+        <v>1.1051</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2486</v>
+        <v>-0.1142</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9304</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8842</v>
+        <v>0.5639</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7531</v>
+        <v>1.3992</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8689</v>
+        <v>-0.8353</v>
       </c>
       <c r="G7" t="n">
         <v>0.1422</v>
@@ -1000,13 +1000,13 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2781</v>
+        <v>-0.0422</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3383</v>
+        <v>-0.0156</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0602</v>
+        <v>-0.0266</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1131</v>
+        <v>-0.9712</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1778</v>
+        <v>-1.1032</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.132</v>
       </c>
       <c r="G8" t="n">
         <v>0.0795</v>
@@ -1078,13 +1078,13 @@
         <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5843</v>
+        <v>-0.4424</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4481</v>
+        <v>-0.3734</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1362</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7114</v>
+        <v>-1.4755</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0094</v>
+        <v>0.2453</v>
       </c>
       <c r="F9" t="n">
         <v>-1.7207</v>
@@ -1156,10 +1156,10 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.2948</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="U9" t="n">
         <v>-0.1573</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1935</v>
+        <v>-2.407</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.6221</v>
+        <v>-6.634</v>
       </c>
       <c r="F10" t="n">
-        <v>4.4286</v>
+        <v>4.227</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3161</v>
@@ -1234,13 +1234,13 @@
         <v>2.5515</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3003</v>
+        <v>1.0868</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8417</v>
+        <v>0.8298</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4586</v>
+        <v>0.257</v>
       </c>
       <c r="V10" t="n">
         <v>0.1418</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6268</v>
+        <v>-3.273</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2422</v>
+        <v>-0.8883</v>
       </c>
       <c r="F11" t="n">
         <v>-2.3846</v>
@@ -1312,10 +1312,10 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.224</v>
+        <v>0.1298</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.224</v>
+        <v>0.1298</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8043</v>
+        <v>-3.3518</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8691</v>
+        <v>-3.4838</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.132</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1454</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8909</v>
+        <v>-0.4384</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4402</v>
+        <v>-0.0549</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4507</v>
+        <v>-0.3835</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.726</v>
+        <v>-4.9511</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.1883</v>
+        <v>-3.4806</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5377</v>
+        <v>-1.4705</v>
       </c>
       <c r="G13" t="n">
         <v>-4.235</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0244</v>
+        <v>-0.2495</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5975</v>
+        <v>0.1103</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.427</v>
+        <v>-0.3598</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9304</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.6564</v>
+        <v>14.7764</v>
       </c>
       <c r="E14" t="n">
-        <v>2.312200000000002</v>
+        <v>3.432399999999997</v>
       </c>
       <c r="F14" t="n">
-        <v>11.3441</v>
+        <v>11.3442</v>
       </c>
       <c r="G14" t="n">
-        <v>6.522699999999999</v>
+        <v>6.522699999999998</v>
       </c>
       <c r="H14" t="n">
         <v>-1.3569</v>
@@ -1519,7 +1519,7 @@
         <v>7.879899999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>7.7412</v>
+        <v>7.741199999999997</v>
       </c>
       <c r="K14" t="n">
         <v>8.4787</v>
@@ -1546,13 +1546,13 @@
         <v>20.8759</v>
       </c>
       <c r="S14" t="n">
-        <v>3.479299999999999</v>
+        <v>4.599400000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>4.3665</v>
+        <v>5.4869</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8872999999999998</v>
+        <v>-0.8874</v>
       </c>
       <c r="V14" t="n">
         <v>-2.144400000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1932</v>
+        <v>4.677</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4044</v>
+        <v>2.8762</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7888</v>
+        <v>1.8008</v>
       </c>
       <c r="G15" t="n">
         <v>2.4831</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8623</v>
+        <v>-0.3785</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8883</v>
+        <v>-0.4165</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0259</v>
+        <v>0.038</v>
       </c>
       <c r="V15" t="n">
         <v>3.5002</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>L. STEVENS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6634</v>
+        <v>0.6605</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4489</v>
+        <v>1.084</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2145</v>
+        <v>-0.4235</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5942</v>
+        <v>0.7881</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0492</v>
+        <v>0.8583</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.455</v>
+        <v>-0.0702</v>
       </c>
       <c r="J16" t="n">
-        <v>1.502</v>
+        <v>0.8672</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4284</v>
+        <v>1.6168</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0736</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.0791</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3792</v>
+        <v>-0.7584</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5286</v>
+        <v>0.6793</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8552</v>
+        <v>-0.5219</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1246</v>
+        <v>-0.2317</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7306</v>
+        <v>-0.2902</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1418</v>
+        <v>0.3943</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>1.6083</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. STEVENS</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6662</v>
+        <v>0.5188</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4379</v>
+        <v>-0.2588</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7716</v>
+        <v>0.7776</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7881</v>
+        <v>0.5942</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8583</v>
+        <v>1.0492</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0702</v>
+        <v>-0.455</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8672</v>
+        <v>1.502</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6168</v>
+        <v>1.4284</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.0736</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0791</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7584</v>
+        <v>-0.3792</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6793</v>
+        <v>-0.5286</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5162</v>
+        <v>0.7106</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1221</v>
+        <v>0.4169</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6383</v>
+        <v>0.2937</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3943</v>
+        <v>0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6083</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5796</v>
+        <v>0.4623</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2205</v>
+        <v>0.3385</v>
       </c>
       <c r="F18" t="n">
-        <v>0.359</v>
+        <v>0.1238</v>
       </c>
       <c r="G18" t="n">
         <v>0.0567</v>
@@ -1858,13 +1858,13 @@
         <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2008</v>
+        <v>0.0835</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5228</v>
+        <v>-0.4048</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7235</v>
+        <v>0.4883</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1418</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5474</v>
+        <v>-0.2612</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0581</v>
+        <v>0.3504</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5108</v>
+        <v>-0.6116</v>
       </c>
       <c r="G19" t="n">
         <v>0.1349</v>
@@ -1936,13 +1936,13 @@
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6445</v>
+        <v>-0.1641</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2072</v>
+        <v>0.4995</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5627</v>
+        <v>-0.6636</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0353</v>
+        <v>-0.914</v>
       </c>
       <c r="E20" t="n">
-        <v>0.008800000000000001</v>
+        <v>-1.2212</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0441</v>
+        <v>0.3072</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4614</v>
+        <v>-0.7388</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5317</v>
+        <v>1.0612</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0703</v>
+        <v>-1.8001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1107</v>
+        <v>0.8229</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0371</v>
+        <v>1.462</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0736</v>
+        <v>-0.6391</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-1.5617</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5688</v>
+        <v>-0.4008</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0033</v>
+        <v>-1.1609</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0584</v>
+        <v>0.4305</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0578</v>
+        <v>0.2754</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1163</v>
+        <v>0.1551</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2836</v>
+        <v>-0.1418</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2836</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3515</v>
+        <v>-1.367</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4571</v>
+        <v>-0.581</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1055</v>
+        <v>-0.786</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7388</v>
+        <v>-0.4614</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0612</v>
+        <v>-0.5317</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8001</v>
+        <v>0.0703</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8229</v>
+        <v>0.1107</v>
       </c>
       <c r="K21" t="n">
-        <v>1.462</v>
+        <v>0.0371</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6391</v>
+        <v>0.0736</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5617</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4008</v>
+        <v>-0.5688</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1609</v>
+        <v>-0.0033</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.007</v>
+        <v>-0.3901</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0395</v>
+        <v>0.4681</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0466</v>
+        <v>-0.8582</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1418</v>
+        <v>-0.2836</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7048</v>
+        <v>-1.857</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6264</v>
+        <v>-0.9802999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0784</v>
+        <v>-0.8767</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3214</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2249</v>
+        <v>0.0727</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9006</v>
+        <v>0.5467</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6756</v>
+        <v>-0.474</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7545</v>
+        <v>-2.6479</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.008</v>
+        <v>-1.126</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7464</v>
+        <v>-1.522</v>
       </c>
       <c r="G23" t="n">
         <v>0.06370000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8672</v>
+        <v>-0.7606000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1845</v>
+        <v>-0.3025</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6827</v>
+        <v>-0.4582</v>
       </c>
       <c r="V23" t="n">
         <v>-1.719</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8933</v>
+        <v>-3.5959</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.0203</v>
+        <v>-4.1382</v>
       </c>
       <c r="F24" t="n">
-        <v>0.127</v>
+        <v>0.5424</v>
       </c>
       <c r="G24" t="n">
         <v>-2.172</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4714</v>
+        <v>-0.174</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0395</v>
+        <v>-0.0784</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5109</v>
+        <v>-0.0955</v>
       </c>
       <c r="V24" t="n">
         <v>0.1418</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.2524</v>
+        <v>-3.6132</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.4435</v>
+        <v>-3.264</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8089</v>
+        <v>-0.3492</v>
       </c>
       <c r="G25" t="n">
         <v>-3.9003</v>
@@ -2404,13 +2404,13 @@
         <v>1.8556</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.2672</v>
+        <v>-0.628</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0455</v>
+        <v>0.134</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.2217</v>
+        <v>-0.762</v>
       </c>
       <c r="V25" t="n">
         <v>2.5387</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.3141</v>
+        <v>-4.146</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.3674</v>
+        <v>-4.4238</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0532</v>
+        <v>0.2777</v>
       </c>
       <c r="G26" t="n">
         <v>-2.0495</v>
@@ -2482,13 +2482,13 @@
         <v>1.6237</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.3548</v>
+        <v>-0.1867</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.963</v>
+        <v>-0.0193</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3918</v>
+        <v>-0.1674</v>
       </c>
       <c r="V26" t="n">
         <v>-1.214</v>
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-13.6561</v>
+        <v>-12.0836</v>
       </c>
       <c r="E27" t="n">
-        <v>-11.3441</v>
+        <v>-11.3442</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.3122</v>
+        <v>-0.7395000000000003</v>
       </c>
       <c r="G27" t="n">
-        <v>-6.522700000000001</v>
+        <v>-6.5227</v>
       </c>
       <c r="H27" t="n">
         <v>1.3571</v>
@@ -2545,7 +2545,7 @@
         <v>-7.741300000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>-8.478499999999999</v>
+        <v>-8.4785</v>
       </c>
       <c r="O27" t="n">
         <v>0.7373999999999998</v>
@@ -2560,13 +2560,13 @@
         <v>15.0769</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.4791</v>
+        <v>-1.9066</v>
       </c>
       <c r="T27" t="n">
-        <v>0.8871999999999997</v>
+        <v>0.8874</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.3666</v>
+        <v>-2.794</v>
       </c>
       <c r="V27" t="n">
         <v>2.1444</v>
